--- a/Excel/InfiniteConfig.xlsx
+++ b/Excel/InfiniteConfig.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="336">
   <si>
     <t>ID</t>
   </si>
@@ -1004,6 +1004,36 @@
   </si>
   <si>
     <t>1E+310</t>
+  </si>
+  <si>
+    <t>1E+405</t>
+  </si>
+  <si>
+    <t>1E+320</t>
+  </si>
+  <si>
+    <t>1E+411</t>
+  </si>
+  <si>
+    <t>1E+330</t>
+  </si>
+  <si>
+    <t>1E+417</t>
+  </si>
+  <si>
+    <t>1E+340</t>
+  </si>
+  <si>
+    <t>1E+423</t>
+  </si>
+  <si>
+    <t>1E+350</t>
+  </si>
+  <si>
+    <t>1E+429</t>
+  </si>
+  <si>
+    <t>1E+360</t>
   </si>
   <si>
     <t>1E+1</t>
@@ -5011,15 +5041,15 @@
         <v>22000</v>
       </c>
       <c r="T36" s="15">
-        <f t="shared" ref="T36:T95" si="16">T35+3000</f>
+        <f t="shared" ref="T36:T100" si="16">T35+3000</f>
         <v>22000</v>
       </c>
       <c r="U36" s="15">
-        <f t="shared" ref="U36:U95" si="17">U35+2000</f>
+        <f t="shared" ref="U36:U99" si="17">U35+2000</f>
         <v>14000</v>
       </c>
       <c r="V36" s="15">
-        <f t="shared" ref="V36:V95" si="18">V35+2000</f>
+        <f t="shared" ref="V36:V99" si="18">V35+2000</f>
         <v>14000</v>
       </c>
       <c r="W36" s="15">
@@ -5027,7 +5057,7 @@
         <v>165</v>
       </c>
       <c r="X36" s="15">
-        <f t="shared" ref="X36:X95" si="19">X35+15</f>
+        <f t="shared" ref="X36:X99" si="19">X35+15</f>
         <v>130</v>
       </c>
       <c r="Y36" s="15">
@@ -5111,7 +5141,7 @@
         <v>16000</v>
       </c>
       <c r="W37" s="15">
-        <f t="shared" ref="W37:W95" si="20">W36+20</f>
+        <f t="shared" ref="W37:W100" si="20">W36+20</f>
         <v>185</v>
       </c>
       <c r="X37" s="15">
@@ -7207,7 +7237,7 @@
         <v>175</v>
       </c>
       <c r="S61" s="4">
-        <f t="shared" ref="S61:S95" si="21">S60+10000</f>
+        <f t="shared" ref="S61:S100" si="21">S60+10000</f>
         <v>104000</v>
       </c>
       <c r="T61" s="4">
@@ -7644,7 +7674,7 @@
         <v>100</v>
       </c>
       <c r="R66" s="1">
-        <f t="shared" ref="R66:R95" si="22">R65+5</f>
+        <f t="shared" ref="R66:R100" si="22">R65+5</f>
         <v>180</v>
       </c>
       <c r="S66" s="15">
@@ -8045,11 +8075,11 @@
         <v>66</v>
       </c>
       <c r="D71" s="1">
-        <f t="shared" ref="D71:D95" si="23">E70+1</f>
+        <f t="shared" ref="D71:D100" si="23">E70+1</f>
         <v>6501</v>
       </c>
       <c r="E71" s="1">
-        <f t="shared" ref="E71:E95" si="24">E70+100</f>
+        <f t="shared" ref="E71:E100" si="24">E70+100</f>
         <v>6600</v>
       </c>
       <c r="F71" s="26" t="s">
@@ -10266,86 +10296,501 @@
       </c>
     </row>
     <row r="96" customHeight="1" spans="3:28">
-      <c r="P96" s="1"/>
-      <c r="Q96" s="1"/>
-      <c r="R96" s="1"/>
-    </row>
-    <row r="97" customHeight="1" spans="16:18">
-      <c r="P97" s="1"/>
-      <c r="Q97" s="1"/>
-      <c r="R97" s="1"/>
-    </row>
-    <row r="98" customHeight="1" spans="16:18">
-      <c r="P98" s="1"/>
-      <c r="Q98" s="1"/>
-      <c r="R98" s="1"/>
-    </row>
-    <row r="99" customHeight="1" spans="16:18">
-      <c r="P99" s="1"/>
-      <c r="Q99" s="1"/>
-      <c r="R99" s="1"/>
-    </row>
-    <row r="100" customHeight="1" spans="16:18">
-      <c r="P100" s="1"/>
-      <c r="Q100" s="1"/>
-      <c r="R100" s="1"/>
-    </row>
-    <row r="101" customHeight="1" spans="16:18">
+      <c r="C96" s="1">
+        <v>91</v>
+      </c>
+      <c r="D96" s="1">
+        <f t="shared" si="23"/>
+        <v>9001</v>
+      </c>
+      <c r="E96" s="1">
+        <f t="shared" si="24"/>
+        <v>9100</v>
+      </c>
+      <c r="F96" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="G96" s="14">
+        <v>1000</v>
+      </c>
+      <c r="H96" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="I96" s="14">
+        <v>0</v>
+      </c>
+      <c r="J96" s="26" t="s">
+        <v>323</v>
+      </c>
+      <c r="K96" s="14">
+        <v>1000</v>
+      </c>
+      <c r="L96" s="26" t="s">
+        <v>324</v>
+      </c>
+      <c r="M96" s="14">
+        <v>1000</v>
+      </c>
+      <c r="N96" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="O96" s="14">
+        <v>1000</v>
+      </c>
+      <c r="P96" s="26" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q96" s="1">
+        <v>1000</v>
+      </c>
+      <c r="R96" s="1">
+        <v>330</v>
+      </c>
+      <c r="S96" s="15">
+        <f t="shared" si="21"/>
+        <v>454000</v>
+      </c>
+      <c r="T96" s="15">
+        <f t="shared" si="16"/>
+        <v>209000</v>
+      </c>
+      <c r="U96" s="15">
+        <f t="shared" si="17"/>
+        <v>134000</v>
+      </c>
+      <c r="V96" s="15">
+        <f t="shared" si="18"/>
+        <v>134000</v>
+      </c>
+      <c r="W96" s="15">
+        <f t="shared" si="20"/>
+        <v>1365</v>
+      </c>
+      <c r="X96" s="15">
+        <f t="shared" si="19"/>
+        <v>1030</v>
+      </c>
+      <c r="Y96" s="15">
+        <v>99.4</v>
+      </c>
+      <c r="Z96" s="15">
+        <v>99.99999</v>
+      </c>
+      <c r="AA96" s="13">
+        <v>3.2e+18</v>
+      </c>
+      <c r="AB96" s="13">
+        <v>3.2e+18</v>
+      </c>
+    </row>
+    <row r="97" customHeight="1" spans="3:28">
+      <c r="C97" s="1">
+        <v>92</v>
+      </c>
+      <c r="D97" s="1">
+        <f t="shared" si="23"/>
+        <v>9101</v>
+      </c>
+      <c r="E97" s="1">
+        <f t="shared" si="24"/>
+        <v>9200</v>
+      </c>
+      <c r="F97" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="G97" s="14">
+        <v>1000</v>
+      </c>
+      <c r="H97" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="I97" s="14">
+        <v>0</v>
+      </c>
+      <c r="J97" s="26" t="s">
+        <v>325</v>
+      </c>
+      <c r="K97" s="14">
+        <v>1000</v>
+      </c>
+      <c r="L97" s="26" t="s">
+        <v>326</v>
+      </c>
+      <c r="M97" s="14">
+        <v>1000</v>
+      </c>
+      <c r="N97" s="26" t="s">
+        <v>278</v>
+      </c>
+      <c r="O97" s="14">
+        <v>1000</v>
+      </c>
+      <c r="P97" s="26" t="s">
+        <v>278</v>
+      </c>
+      <c r="Q97" s="1">
+        <v>1000</v>
+      </c>
+      <c r="R97" s="1">
+        <v>330</v>
+      </c>
+      <c r="S97" s="15">
+        <f t="shared" si="21"/>
+        <v>464000</v>
+      </c>
+      <c r="T97" s="15">
+        <f t="shared" si="16"/>
+        <v>212000</v>
+      </c>
+      <c r="U97" s="15">
+        <f t="shared" si="17"/>
+        <v>136000</v>
+      </c>
+      <c r="V97" s="15">
+        <f t="shared" si="18"/>
+        <v>136000</v>
+      </c>
+      <c r="W97" s="15">
+        <f t="shared" si="20"/>
+        <v>1385</v>
+      </c>
+      <c r="X97" s="15">
+        <f t="shared" si="19"/>
+        <v>1045</v>
+      </c>
+      <c r="Y97" s="15">
+        <v>99.4</v>
+      </c>
+      <c r="Z97" s="15">
+        <v>99.99999</v>
+      </c>
+      <c r="AA97" s="13">
+        <v>3.3e+18</v>
+      </c>
+      <c r="AB97" s="13">
+        <v>3.3e+18</v>
+      </c>
+    </row>
+    <row r="98" customHeight="1" spans="3:28">
+      <c r="C98" s="1">
+        <v>93</v>
+      </c>
+      <c r="D98" s="1">
+        <f t="shared" si="23"/>
+        <v>9201</v>
+      </c>
+      <c r="E98" s="1">
+        <f t="shared" si="24"/>
+        <v>9300</v>
+      </c>
+      <c r="F98" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="G98" s="14">
+        <v>1000</v>
+      </c>
+      <c r="H98" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="I98" s="14">
+        <v>0</v>
+      </c>
+      <c r="J98" s="26" t="s">
+        <v>327</v>
+      </c>
+      <c r="K98" s="14">
+        <v>1000</v>
+      </c>
+      <c r="L98" s="26" t="s">
+        <v>328</v>
+      </c>
+      <c r="M98" s="14">
+        <v>1000</v>
+      </c>
+      <c r="N98" s="26" t="s">
+        <v>282</v>
+      </c>
+      <c r="O98" s="14">
+        <v>1000</v>
+      </c>
+      <c r="P98" s="26" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q98" s="1">
+        <v>1000</v>
+      </c>
+      <c r="R98" s="1">
+        <v>330</v>
+      </c>
+      <c r="S98" s="15">
+        <f t="shared" si="21"/>
+        <v>474000</v>
+      </c>
+      <c r="T98" s="15">
+        <f t="shared" si="16"/>
+        <v>215000</v>
+      </c>
+      <c r="U98" s="15">
+        <f t="shared" si="17"/>
+        <v>138000</v>
+      </c>
+      <c r="V98" s="15">
+        <f t="shared" si="18"/>
+        <v>138000</v>
+      </c>
+      <c r="W98" s="15">
+        <f t="shared" si="20"/>
+        <v>1405</v>
+      </c>
+      <c r="X98" s="15">
+        <f t="shared" si="19"/>
+        <v>1060</v>
+      </c>
+      <c r="Y98" s="15">
+        <v>99.4</v>
+      </c>
+      <c r="Z98" s="15">
+        <v>99.99999</v>
+      </c>
+      <c r="AA98" s="13">
+        <v>3.4e+18</v>
+      </c>
+      <c r="AB98" s="13">
+        <v>3.4e+18</v>
+      </c>
+    </row>
+    <row r="99" customHeight="1" spans="3:28">
+      <c r="C99" s="1">
+        <v>94</v>
+      </c>
+      <c r="D99" s="1">
+        <f t="shared" si="23"/>
+        <v>9301</v>
+      </c>
+      <c r="E99" s="1">
+        <f t="shared" si="24"/>
+        <v>9400</v>
+      </c>
+      <c r="F99" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="G99" s="14">
+        <v>1000</v>
+      </c>
+      <c r="H99" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="I99" s="14">
+        <v>0</v>
+      </c>
+      <c r="J99" s="26" t="s">
+        <v>329</v>
+      </c>
+      <c r="K99" s="14">
+        <v>1000</v>
+      </c>
+      <c r="L99" s="26" t="s">
+        <v>330</v>
+      </c>
+      <c r="M99" s="14">
+        <v>1000</v>
+      </c>
+      <c r="N99" s="26" t="s">
+        <v>285</v>
+      </c>
+      <c r="O99" s="14">
+        <v>1000</v>
+      </c>
+      <c r="P99" s="26" t="s">
+        <v>285</v>
+      </c>
+      <c r="Q99" s="1">
+        <v>1000</v>
+      </c>
+      <c r="R99" s="1">
+        <v>330</v>
+      </c>
+      <c r="S99" s="15">
+        <f t="shared" si="21"/>
+        <v>484000</v>
+      </c>
+      <c r="T99" s="15">
+        <f t="shared" si="16"/>
+        <v>218000</v>
+      </c>
+      <c r="U99" s="15">
+        <f t="shared" si="17"/>
+        <v>140000</v>
+      </c>
+      <c r="V99" s="15">
+        <f t="shared" si="18"/>
+        <v>140000</v>
+      </c>
+      <c r="W99" s="15">
+        <f t="shared" si="20"/>
+        <v>1425</v>
+      </c>
+      <c r="X99" s="15">
+        <f t="shared" si="19"/>
+        <v>1075</v>
+      </c>
+      <c r="Y99" s="15">
+        <v>99.4</v>
+      </c>
+      <c r="Z99" s="15">
+        <v>99.99999</v>
+      </c>
+      <c r="AA99" s="13">
+        <v>3.5e+18</v>
+      </c>
+      <c r="AB99" s="13">
+        <v>3.5e+18</v>
+      </c>
+    </row>
+    <row r="100" customHeight="1" spans="3:28">
+      <c r="C100" s="1">
+        <v>95</v>
+      </c>
+      <c r="D100" s="1">
+        <f t="shared" si="23"/>
+        <v>9401</v>
+      </c>
+      <c r="E100" s="1">
+        <f t="shared" si="24"/>
+        <v>9500</v>
+      </c>
+      <c r="F100" s="26" t="s">
+        <v>311</v>
+      </c>
+      <c r="G100" s="14">
+        <v>1000</v>
+      </c>
+      <c r="H100" s="26" t="s">
+        <v>239</v>
+      </c>
+      <c r="I100" s="14">
+        <v>0</v>
+      </c>
+      <c r="J100" s="26" t="s">
+        <v>331</v>
+      </c>
+      <c r="K100" s="14">
+        <v>1000</v>
+      </c>
+      <c r="L100" s="26" t="s">
+        <v>332</v>
+      </c>
+      <c r="M100" s="14">
+        <v>1000</v>
+      </c>
+      <c r="N100" s="26" t="s">
+        <v>287</v>
+      </c>
+      <c r="O100" s="14">
+        <v>1000</v>
+      </c>
+      <c r="P100" s="26" t="s">
+        <v>287</v>
+      </c>
+      <c r="Q100" s="1">
+        <v>1000</v>
+      </c>
+      <c r="R100" s="1">
+        <v>330</v>
+      </c>
+      <c r="S100" s="15">
+        <f t="shared" si="21"/>
+        <v>494000</v>
+      </c>
+      <c r="T100" s="15">
+        <f t="shared" si="16"/>
+        <v>221000</v>
+      </c>
+      <c r="U100" s="15">
+        <f>U99+2000</f>
+        <v>142000</v>
+      </c>
+      <c r="V100" s="15">
+        <f>V99+2000</f>
+        <v>142000</v>
+      </c>
+      <c r="W100" s="15">
+        <f t="shared" si="20"/>
+        <v>1445</v>
+      </c>
+      <c r="X100" s="15">
+        <f>X99+15</f>
+        <v>1090</v>
+      </c>
+      <c r="Y100" s="15">
+        <v>99.4</v>
+      </c>
+      <c r="Z100" s="15">
+        <v>99.99999</v>
+      </c>
+      <c r="AA100" s="13">
+        <v>3.6e+18</v>
+      </c>
+      <c r="AB100" s="13">
+        <v>3.6e+18</v>
+      </c>
+    </row>
+    <row r="101" customHeight="1" spans="3:28">
       <c r="P101" s="1"/>
       <c r="Q101" s="1"/>
       <c r="R101" s="1"/>
     </row>
-    <row r="102" customHeight="1" spans="16:18">
+    <row r="102" customHeight="1" spans="3:28">
       <c r="P102" s="1"/>
       <c r="Q102" s="1"/>
       <c r="R102" s="1"/>
     </row>
-    <row r="103" customHeight="1" spans="16:18">
+    <row r="103" customHeight="1" spans="3:28">
       <c r="P103" s="1"/>
       <c r="Q103" s="1"/>
       <c r="R103" s="1"/>
     </row>
-    <row r="104" customHeight="1" spans="16:18">
+    <row r="104" customHeight="1" spans="3:28">
       <c r="P104" s="1"/>
       <c r="Q104" s="1"/>
       <c r="R104" s="1"/>
     </row>
-    <row r="105" customHeight="1" spans="16:18">
+    <row r="105" customHeight="1" spans="3:28">
       <c r="P105" s="1"/>
       <c r="Q105" s="1"/>
       <c r="R105" s="1"/>
     </row>
-    <row r="106" customHeight="1" spans="16:18">
+    <row r="106" customHeight="1" spans="3:28">
       <c r="P106" s="1"/>
       <c r="Q106" s="1"/>
       <c r="R106" s="1"/>
     </row>
-    <row r="107" customHeight="1" spans="16:18">
+    <row r="107" customHeight="1" spans="3:28">
       <c r="P107" s="1"/>
       <c r="Q107" s="1"/>
       <c r="R107" s="1"/>
     </row>
-    <row r="108" customHeight="1" spans="16:18">
+    <row r="108" customHeight="1" spans="3:28">
       <c r="P108" s="1"/>
       <c r="Q108" s="1"/>
       <c r="R108" s="1"/>
     </row>
-    <row r="109" customHeight="1" spans="16:18">
+    <row r="109" customHeight="1" spans="3:28">
       <c r="P109" s="1"/>
       <c r="Q109" s="1"/>
       <c r="R109" s="1"/>
     </row>
-    <row r="110" customHeight="1" spans="16:18">
+    <row r="110" customHeight="1" spans="3:28">
       <c r="P110" s="1"/>
       <c r="Q110" s="1"/>
       <c r="R110" s="1"/>
     </row>
-    <row r="111" customHeight="1" spans="16:18">
+    <row r="111" customHeight="1" spans="3:28">
       <c r="P111" s="1"/>
       <c r="Q111" s="1"/>
       <c r="R111" s="1"/>
     </row>
-    <row r="112" customHeight="1" spans="16:18">
+    <row r="112" customHeight="1" spans="3:28">
       <c r="P112" s="1"/>
       <c r="Q112" s="1"/>
       <c r="R112" s="1"/>
@@ -10692,21 +11137,21 @@
     </row>
     <row r="181" customHeight="1" spans="16:18">
       <c r="P181" s="31" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="Q181" s="19"/>
       <c r="R181" s="19"/>
     </row>
     <row r="182" customHeight="1" spans="16:18">
       <c r="P182" s="32" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="Q182" s="12"/>
       <c r="R182" s="12"/>
     </row>
     <row r="183" customHeight="1" spans="16:18">
       <c r="P183" s="32" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="Q183" s="12"/>
       <c r="R183" s="12"/>
